--- a/ExportExcel/Filter Product Tests.xlsx
+++ b/ExportExcel/Filter Product Tests.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="27">
   <si>
     <t>STT</t>
   </si>
@@ -38,22 +38,61 @@
     <t/>
   </si>
   <si>
-    <t>FAILED</t>
-  </si>
-  <si>
-    <t>1 ms</t>
-  </si>
-  <si>
-    <t>Cannot invoke "org.openqa.selenium.support.ui.WebDriverWait.until(java.util.function.Function)" because "this.wait" is null</t>
-  </si>
-  <si>
-    <t>0 ms</t>
+    <t>PASSED</t>
+  </si>
+  <si>
+    <t>108 ms</t>
+  </si>
+  <si>
+    <t>124 ms</t>
+  </si>
+  <si>
+    <t>129 ms</t>
+  </si>
+  <si>
+    <t>106 ms</t>
+  </si>
+  <si>
+    <t>628 ms</t>
+  </si>
+  <si>
+    <t>143 ms</t>
+  </si>
+  <si>
+    <t>111 ms</t>
+  </si>
+  <si>
+    <t>631 ms</t>
+  </si>
+  <si>
+    <t>104 ms</t>
+  </si>
+  <si>
+    <t>626 ms</t>
   </si>
   <si>
     <t>testSelectMultipleColorFilters</t>
   </si>
   <si>
+    <t>26415 ms</t>
+  </si>
+  <si>
     <t>testPriceFilter</t>
+  </si>
+  <si>
+    <t>2497 ms</t>
+  </si>
+  <si>
+    <t>2440 ms</t>
+  </si>
+  <si>
+    <t>2441 ms</t>
+  </si>
+  <si>
+    <t>2448 ms</t>
+  </si>
+  <si>
+    <t>2427 ms</t>
   </si>
 </sst>
 </file>
@@ -126,9 +165,9 @@
     <col min="1" max="1" width="3.76171875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="24.7734375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="9.52734375" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="6.484375" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="7.08203125" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="13.2109375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="100.69140625" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="18.703125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -161,14 +200,14 @@
       <c r="C2" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D2" t="s" s="2">
+      <c r="D2" t="s" s="1">
         <v>8</v>
       </c>
       <c r="E2" t="s" s="0">
         <v>9</v>
       </c>
       <c r="F2" t="s" s="0">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -181,14 +220,14 @@
       <c r="C3" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D3" t="s" s="2">
+      <c r="D3" t="s" s="1">
         <v>8</v>
       </c>
       <c r="E3" t="s" s="0">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s" s="0">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4">
@@ -201,14 +240,14 @@
       <c r="C4" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D4" t="s" s="2">
+      <c r="D4" t="s" s="1">
         <v>8</v>
       </c>
       <c r="E4" t="s" s="0">
         <v>11</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
@@ -221,14 +260,14 @@
       <c r="C5" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D5" t="s" s="2">
+      <c r="D5" t="s" s="1">
         <v>8</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -241,14 +280,14 @@
       <c r="C6" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D6" t="s" s="2">
+      <c r="D6" t="s" s="1">
         <v>8</v>
       </c>
       <c r="E6" t="s" s="0">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F6" t="s" s="0">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7">
@@ -261,14 +300,14 @@
       <c r="C7" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D7" t="s" s="2">
+      <c r="D7" t="s" s="1">
         <v>8</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F7" t="s" s="0">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -281,14 +320,14 @@
       <c r="C8" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D8" t="s" s="2">
+      <c r="D8" t="s" s="1">
         <v>8</v>
       </c>
       <c r="E8" t="s" s="0">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F8" t="s" s="0">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -301,14 +340,14 @@
       <c r="C9" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D9" t="s" s="2">
+      <c r="D9" t="s" s="1">
         <v>8</v>
       </c>
       <c r="E9" t="s" s="0">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="F9" t="s" s="0">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
@@ -321,14 +360,14 @@
       <c r="C10" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D10" t="s" s="2">
+      <c r="D10" t="s" s="1">
         <v>8</v>
       </c>
       <c r="E10" t="s" s="0">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F10" t="s" s="0">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11">
@@ -341,14 +380,14 @@
       <c r="C11" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D11" t="s" s="2">
+      <c r="D11" t="s" s="1">
         <v>8</v>
       </c>
       <c r="E11" t="s" s="0">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F11" t="s" s="0">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12">
@@ -356,19 +395,19 @@
         <v>11.0</v>
       </c>
       <c r="B12" t="s" s="0">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C12" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D12" t="s" s="2">
+      <c r="D12" t="s" s="1">
         <v>8</v>
       </c>
       <c r="E12" t="s" s="0">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F12" t="s" s="0">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -376,19 +415,19 @@
         <v>12.0</v>
       </c>
       <c r="B13" t="s" s="0">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C13" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D13" t="s" s="2">
+      <c r="D13" t="s" s="1">
         <v>8</v>
       </c>
       <c r="E13" t="s" s="0">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F13" t="s" s="0">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14">
@@ -396,19 +435,19 @@
         <v>13.0</v>
       </c>
       <c r="B14" t="s" s="0">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C14" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D14" t="s" s="2">
+      <c r="D14" t="s" s="1">
         <v>8</v>
       </c>
       <c r="E14" t="s" s="0">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F14" t="s" s="0">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -416,19 +455,19 @@
         <v>14.0</v>
       </c>
       <c r="B15" t="s" s="0">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C15" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D15" t="s" s="2">
+      <c r="D15" t="s" s="1">
         <v>8</v>
       </c>
       <c r="E15" t="s" s="0">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="F15" t="s" s="0">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -436,19 +475,19 @@
         <v>15.0</v>
       </c>
       <c r="B16" t="s" s="0">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C16" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D16" t="s" s="2">
+      <c r="D16" t="s" s="1">
         <v>8</v>
       </c>
       <c r="E16" t="s" s="0">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="F16" t="s" s="0">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -456,19 +495,19 @@
         <v>16.0</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C17" t="s" s="0">
         <v>7</v>
       </c>
-      <c r="D17" t="s" s="2">
+      <c r="D17" t="s" s="1">
         <v>8</v>
       </c>
       <c r="E17" t="s" s="0">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F17" t="s" s="0">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
